--- a/excel_templates/tirtl_manifest_template.xlsx
+++ b/excel_templates/tirtl_manifest_template.xlsx
@@ -1210,12 +1210,12 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>Optional plate coordinate for the well represented by the FASTQ. Paired R1/R2 files from the same well must share the same value when provided. Leave blank for raw-mode submissions containing only a FASTQ pair.</t>
+          <t>Optional plate coordinate for the well represented by the FASTQ. Use the zero-padded format A01 through P24. Paired R1/R2 files from the same well must share the same value when provided. Leave blank for raw-mode submissions containing only a FASTQ pair.</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>Plate coordinates A1 through P24</t>
+          <t>Plate coordinates A01 through P24</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
@@ -1225,7 +1225,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A01</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr"/>

--- a/excel_templates/tirtl_manifest_template.xlsx
+++ b/excel_templates/tirtl_manifest_template.xlsx
@@ -1648,7 +1648,7 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>Whether FASTQ or BAM reads are paired end</t>
+          <t>Whether FASTQ reads are paired end</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">

--- a/excel_templates/tirtl_manifest_template.xlsx
+++ b/excel_templates/tirtl_manifest_template.xlsx
@@ -1643,12 +1643,12 @@
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>Whether FASTQ reads are paired end</t>
+          <t>Whether FASTQ reads are paired end. Required when inputs are FASTQ files.</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">

--- a/excel_templates/tirtl_manifest_template.xlsx
+++ b/excel_templates/tirtl_manifest_template.xlsx
@@ -772,7 +772,7 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>"Bone Marrow", "Buffy Coat", "Derived Cell Line", "Not Available", "Not Reported", "Patient Derived Xenograft", "Xenograft", "Patient Derived Organoid", "Peripheral Blood Mononuclear Cells", "Peripheral Whole Blood", "Saliva", "Solid Tissue", "Umbilical Cord Blood", "Patient-Derived T Cells", "Modified T Cells", "Patient-Derived Primary Cells", "iPSC-Derived Organoid", "Cerebrospinal Fluid", "Embryonic Stem Cell Derived Cell Line"</t>
+          <t>"Bone Marrow", "Buffy Coat", "Derived Cell Line", "Not Available", "Not Reported", "Patient Derived Xenograft", "Xenograft", "Patient Derived Organoid", "Peripheral Blood Mononuclear Cells", "Peripheral Whole Blood", "Saliva", "Solid Tissue", "Umbilical Cord Blood", "Patient-Derived T Cells", "Modified T Cells", "Patient-Derived Primary Cells", "iPSC-Derived Organoid", "Cerebrospinal Fluid", "Embryonic Stem Cell Derived Cell Line", "Extracellular Vesicles"</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -2421,7 +2421,7 @@
       <formula1>'Lists'!$B$2:$B$14</formula1>
     </dataValidation>
     <dataValidation sqref="J2:J1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>'Lists'!$C$2:$C$20</formula1>
+      <formula1>'Lists'!$C$2:$C$21</formula1>
     </dataValidation>
     <dataValidation sqref="W2:W1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>'Lists'!$D$2:$D$8</formula1>
@@ -3226,6 +3226,11 @@
       </c>
     </row>
     <row r="21">
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Extracellular Vesicles</t>
+        </is>
+      </c>
       <c r="E21" t="inlineStr">
         <is>
           <t>PED</t>

--- a/excel_templates/tirtl_manifest_template.xlsx
+++ b/excel_templates/tirtl_manifest_template.xlsx
@@ -772,7 +772,7 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>"Bone Marrow", "Buffy Coat", "Derived Cell Line", "Not Available", "Not Reported", "Patient Derived Xenograft", "Xenograft", "Patient Derived Organoid", "Peripheral Blood Mononuclear Cells", "Peripheral Whole Blood", "Saliva", "Solid Tissue", "Umbilical Cord Blood", "Patient-Derived T Cells", "Modified T Cells", "Patient-Derived Primary Cells", "iPSC-Derived Organoid", "Cerebrospinal Fluid", "Embryonic Stem Cell Derived Cell Line", "Extracellular Vesicles"</t>
+          <t>"Bone Marrow", "Buffy Coat", "Derived Cell Line", "Not Available", "Not Reported", "Patient Derived Xenograft", "Xenograft", "Patient Derived Organoid", "Peripheral Blood Mononuclear Cells", "Peripheral Whole Blood", "Saliva", "Solid Tissue", "Umbilical Cord Blood", "Patient-Derived T Cells", "Modified T Cells", "Patient-Derived Primary Cells", "iPSC-Derived Organoid", "Cerebrospinal Fluid", "Embryonic Stem Cell Derived Cell Line"</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -2421,7 +2421,7 @@
       <formula1>'Lists'!$B$2:$B$14</formula1>
     </dataValidation>
     <dataValidation sqref="J2:J1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>'Lists'!$C$2:$C$21</formula1>
+      <formula1>'Lists'!$C$2:$C$20</formula1>
     </dataValidation>
     <dataValidation sqref="W2:W1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>'Lists'!$D$2:$D$8</formula1>
@@ -3226,11 +3226,6 @@
       </c>
     </row>
     <row r="21">
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Extracellular Vesicles</t>
-        </is>
-      </c>
       <c r="E21" t="inlineStr">
         <is>
           <t>PED</t>
